--- a/artifacts/XRP_USDT/metrics/XRP_USDT_metrics.xlsx
+++ b/artifacts/XRP_USDT/metrics/XRP_USDT_metrics.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03858011461614221</v>
+        <v>0.015607793679215</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1964182135550118</v>
+        <v>0.1249311557587418</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1544098380759825</v>
+        <v>0.08298984722186395</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9245355830585466</v>
+        <v>0.9129653163127126</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.270320534592893</v>
+        <v>3.743051513294718</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.077929257641921</v>
+        <v>2.277657327586207</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.931671450446325</v>
+        <v>2.285841010428584</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.029751896241275</v>
+        <v>2.148667959346483</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.885779445714819</v>
+        <v>2.153936907453569</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/XRP_USDT/metrics/XRP_USDT_metrics.xlsx
+++ b/artifacts/XRP_USDT/metrics/XRP_USDT_metrics.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.015607793679215</v>
+        <v>0.01735276348896488</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1249311557587418</v>
+        <v>0.1317298883661748</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08298984722186395</v>
+        <v>0.09140834700580175</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9129653163127126</v>
+        <v>0.8970972725931958</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.743051513294718</v>
+        <v>4.056862507526712</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.277657327586207</v>
+        <v>2.284108189655173</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.285841010428584</v>
+        <v>2.26742886205531</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.148667959346483</v>
+        <v>2.159899421295248</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.153936907453569</v>
+        <v>2.113815881275807</v>
       </c>
     </row>
   </sheetData>
